--- a/Employee_Reports_wi52/Christian Archie Barbosa Niez Q0364.xlsx
+++ b/Employee_Reports_wi52/Christian Archie Barbosa Niez Q0364.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-119</v>
+        <v>-127</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-518</v>
+        <v>-526</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-162</v>
+        <v>-170</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1657,11 +1657,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-122</v>
+        <v>-130</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1706,11 +1706,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-162</v>
+        <v>-170</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1755,11 +1755,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>-120</v>
+        <v>-128</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1804,11 +1804,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-121</v>
+        <v>-129</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1853,11 +1853,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-108</v>
+        <v>-116</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1881,20 +1881,20 @@
       <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>12-Oct-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>12-Oct-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>418</v>
+        <v>726</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>7527</v>
+        <v>7519</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
